--- a/EXCEL/Data/Køn_data/køn.xlsx
+++ b/EXCEL/Data/Køn_data/køn.xlsx
@@ -100,7 +100,7 @@
     <t>Datasæt 02 2016</t>
   </si>
   <si>
-    <t>Kørsel 8.4.2026 13.57.50</t>
+    <t>Kørsel 14.4.2026 12.27.46</t>
   </si>
   <si>
     <t>Undergrænse: 5</t>
@@ -741,31 +741,31 @@
         <v>16</v>
       </c>
       <c r="C4" s="6">
-        <v>119111.44547308423</v>
+        <v>119111.44547308424</v>
       </c>
       <c r="D4" s="7">
         <v>134763</v>
       </c>
       <c r="E4" s="6">
-        <v>119739.2857275901</v>
+        <v>119739.28572759009</v>
       </c>
       <c r="F4" s="7">
         <v>136231</v>
       </c>
       <c r="G4" s="6">
-        <v>120194.39565404375</v>
+        <v>120194.39565404376</v>
       </c>
       <c r="H4" s="7">
         <v>137320</v>
       </c>
       <c r="I4" s="6">
-        <v>121472.76918703031</v>
+        <v>121472.76918703032</v>
       </c>
       <c r="J4" s="7">
         <v>139137</v>
       </c>
       <c r="K4" s="6">
-        <v>122897.81920522815</v>
+        <v>122897.81920522817</v>
       </c>
       <c r="L4" s="7">
         <v>141274</v>
@@ -809,31 +809,31 @@
         <v>16</v>
       </c>
       <c r="C5" s="9">
-        <v>94130.58794739352</v>
+        <v>94130.58794739353</v>
       </c>
       <c r="D5" s="10">
         <v>107035</v>
       </c>
       <c r="E5" s="9">
-        <v>94482.76689262778</v>
+        <v>94482.76689262777</v>
       </c>
       <c r="F5" s="10">
         <v>107911</v>
       </c>
       <c r="G5" s="9">
-        <v>94091.01351280946</v>
+        <v>94091.01351280947</v>
       </c>
       <c r="H5" s="10">
         <v>107999</v>
       </c>
       <c r="I5" s="9">
-        <v>94745.51280507594</v>
+        <v>94745.51280507595</v>
       </c>
       <c r="J5" s="10">
         <v>109050</v>
       </c>
       <c r="K5" s="9">
-        <v>95733.63687880577</v>
+        <v>95733.63687880579</v>
       </c>
       <c r="L5" s="10">
         <v>110680</v>
@@ -863,7 +863,7 @@
         <v>118400</v>
       </c>
       <c r="U5" s="9">
-        <v>100799.49208403839</v>
+        <v>100799.49208403837</v>
       </c>
       <c r="V5" s="10">
         <v>118300</v>
@@ -913,7 +913,7 @@
         <v>12245</v>
       </c>
       <c r="O6" s="6">
-        <v>10685.718602468047</v>
+        <v>10685.718602468045</v>
       </c>
       <c r="P6" s="7">
         <v>12561</v>
@@ -931,7 +931,7 @@
         <v>12375</v>
       </c>
       <c r="U6" s="6">
-        <v>10566.611679092717</v>
+        <v>10566.611679092715</v>
       </c>
       <c r="V6" s="7">
         <v>12383</v>
@@ -963,13 +963,13 @@
         <v>25148</v>
       </c>
       <c r="I7" s="9">
-        <v>21867.49476313534</v>
+        <v>21867.494763135335</v>
       </c>
       <c r="J7" s="10">
         <v>24973</v>
       </c>
       <c r="K7" s="9">
-        <v>22063.14701099467</v>
+        <v>22063.147010994675</v>
       </c>
       <c r="L7" s="10">
         <v>25311</v>
@@ -987,7 +987,7 @@
         <v>28360</v>
       </c>
       <c r="Q7" s="9">
-        <v>23391.614774990227</v>
+        <v>23391.61477499023</v>
       </c>
       <c r="R7" s="10">
         <v>27301</v>
@@ -1019,7 +1019,7 @@
         <v>21977</v>
       </c>
       <c r="E8" s="6">
-        <v>19321.57044485906</v>
+        <v>19321.570444859062</v>
       </c>
       <c r="F8" s="7">
         <v>22039</v>
@@ -1049,19 +1049,19 @@
         <v>24219</v>
       </c>
       <c r="O8" s="6">
-        <v>21097.089695750517</v>
+        <v>21097.08969575052</v>
       </c>
       <c r="P8" s="7">
         <v>25031</v>
       </c>
       <c r="Q8" s="6">
-        <v>20600.534939914938</v>
+        <v>20600.53493991494</v>
       </c>
       <c r="R8" s="7">
         <v>24161</v>
       </c>
       <c r="S8" s="6">
-        <v>20689.906414846308</v>
+        <v>20689.906414846304</v>
       </c>
       <c r="T8" s="7">
         <v>24270</v>
@@ -1099,7 +1099,7 @@
         <v>34465</v>
       </c>
       <c r="I9" s="9">
-        <v>29861.16868665018</v>
+        <v>29861.168686650173</v>
       </c>
       <c r="J9" s="10">
         <v>34819</v>
@@ -1111,7 +1111,7 @@
         <v>34930</v>
       </c>
       <c r="M9" s="9">
-        <v>31496.026477438936</v>
+        <v>31496.02647743894</v>
       </c>
       <c r="N9" s="10">
         <v>37111</v>
@@ -1129,7 +1129,7 @@
         <v>36539</v>
       </c>
       <c r="S9" s="9">
-        <v>31028.014301547984</v>
+        <v>31028.014301547988</v>
       </c>
       <c r="T9" s="10">
         <v>36893</v>
@@ -1161,7 +1161,7 @@
         <v>14209</v>
       </c>
       <c r="G10" s="6">
-        <v>12535.478158393702</v>
+        <v>12535.478158393704</v>
       </c>
       <c r="H10" s="7">
         <v>14160</v>
@@ -1185,7 +1185,7 @@
         <v>15567</v>
       </c>
       <c r="O10" s="6">
-        <v>13661.850328593771</v>
+        <v>13661.850328593773</v>
       </c>
       <c r="P10" s="7">
         <v>16326</v>
@@ -1197,13 +1197,13 @@
         <v>15966</v>
       </c>
       <c r="S10" s="6">
-        <v>13737.649706109736</v>
+        <v>13737.649706109734</v>
       </c>
       <c r="T10" s="7">
         <v>16340</v>
       </c>
       <c r="U10" s="6">
-        <v>13699.150081438269</v>
+        <v>13699.15008143827</v>
       </c>
       <c r="V10" s="7">
         <v>16207</v>
@@ -1223,7 +1223,7 @@
         <v>299</v>
       </c>
       <c r="E11" s="9">
-        <v>233.5696292758112</v>
+        <v>233.56962927581117</v>
       </c>
       <c r="F11" s="10">
         <v>298</v>
@@ -1259,7 +1259,7 @@
         <v>1047</v>
       </c>
       <c r="Q11" s="9">
-        <v>798.5343888311174</v>
+        <v>798.5343888311173</v>
       </c>
       <c r="R11" s="10">
         <v>1069</v>
@@ -1303,7 +1303,7 @@
         <v>29321</v>
       </c>
       <c r="I12" s="6">
-        <v>26727.25638194873</v>
+        <v>26727.256381948733</v>
       </c>
       <c r="J12" s="7">
         <v>30087</v>
@@ -1333,13 +1333,13 @@
         <v>34258</v>
       </c>
       <c r="S12" s="6">
-        <v>30444.397040434957</v>
+        <v>30444.397040434953</v>
       </c>
       <c r="T12" s="7">
         <v>34880</v>
       </c>
       <c r="U12" s="6">
-        <v>30970.580460847825</v>
+        <v>30970.58046084782</v>
       </c>
       <c r="V12" s="7">
         <v>35144</v>
@@ -1371,7 +1371,7 @@
         <v>2646</v>
       </c>
       <c r="I13" s="9">
-        <v>2355.4284995959624</v>
+        <v>2355.428499595963</v>
       </c>
       <c r="J13" s="10">
         <v>2690</v>
@@ -1469,7 +1469,7 @@
         <v>7422</v>
       </c>
       <c r="S14" s="6">
-        <v>6529.44677975743</v>
+        <v>6529.446779757431</v>
       </c>
       <c r="T14" s="7">
         <v>7385</v>
@@ -1543,7 +1543,7 @@
         <v>6909</v>
       </c>
       <c r="U15" s="9">
-        <v>6204.092771429018</v>
+        <v>6204.092771429019</v>
       </c>
       <c r="V15" s="10">
         <v>7037</v>
@@ -1575,7 +1575,7 @@
         <v>10657</v>
       </c>
       <c r="I16" s="6">
-        <v>9606.78169233777</v>
+        <v>9606.781692337769</v>
       </c>
       <c r="J16" s="7">
         <v>10812</v>
@@ -1611,7 +1611,7 @@
         <v>12200</v>
       </c>
       <c r="U16" s="6">
-        <v>10768.619362735528</v>
+        <v>10768.61936273553</v>
       </c>
       <c r="V16" s="7">
         <v>12243</v>
